--- a/2_Planning/Analisis_Cronogramas_CPF2.xlsx
+++ b/2_Planning/Analisis_Cronogramas_CPF2.xlsx
@@ -590,7 +590,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:11   |   Fuente P6: Cronograma CPF2 Rev.0 18-03-26 LB Comercial   |   Fuente ABB: CPF2 Gantt EPC Integrado</t>
+          <t>Generado: 27/05/2026 14:42   |   Fuente P6: Cronograma CPF2 Rev.0 18-03-26 LB Comercial   |   Fuente ABB: CPF2 Gantt EPC Integrado</t>
         </is>
       </c>
     </row>
